--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-physicalexam.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-observation-physicalexam.xlsx
@@ -620,7 +620,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -1395,7 +1395,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
